--- a/TIFF差旅住宿预算.xlsx
+++ b/TIFF差旅住宿预算.xlsx
@@ -20,18 +20,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
-  <si>
-    <t xml:space="preserve">制作公司:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">项目名称:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黑豆 (Black Bean)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">报表名称:</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作公司</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">项目名称</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黑豆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Black Bean)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">报表名称</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
   </si>
   <si>
     <r>
@@ -79,7 +149,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">币种:</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">币种</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
   </si>
   <si>
     <r>
@@ -101,10 +189,28 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">报表日期:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">报表日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-29</t>
   </si>
   <si>
     <r>
@@ -290,13 +396,55 @@
     <t xml:space="preserve">1000</t>
   </si>
   <si>
-    <t xml:space="preserve">机票 FLIGHTS</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">机票 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FLIGHTS</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">100101</t>
   </si>
   <si>
-    <t xml:space="preserve">机票 / Flights — 色珍</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">机票 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Flights — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">色珍</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">电影节</t>
@@ -314,7 +462,31 @@
     <t xml:space="preserve">100102</t>
   </si>
   <si>
-    <t xml:space="preserve">机票 / Flights — 水素</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">机票 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Flights — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">水素</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">水素</t>
@@ -323,13 +495,94 @@
     <t xml:space="preserve">2000</t>
   </si>
   <si>
-    <t xml:space="preserve">住宿 ACCOMMODATION（9.9–9.22 共13晚，USD计价）</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">住宿 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ACCOMMODATION</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Airbnb</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USD</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">计价）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">200101</t>
   </si>
   <si>
-    <t xml:space="preserve">住宿 / Accommodation — 第一段</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">住宿 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Airbnb</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">USD</t>
@@ -342,20 +595,469 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9.9 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起第一段，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
+      <t xml:space="preserve">9.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入住–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">退房共</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晚，均价约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$384.6/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晚（约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">¥2,588/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晚）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">当地杂费 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LOCAL &amp; MISC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">300101</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">餐饮 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Food &amp; Per Diem</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">按天计，待填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300102</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">当地交通 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Local Transport</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">待填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300103</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">签证费 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ Visa Fee</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">加拿大签证，待填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不可预见费 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CONTINGENCY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比例可调整</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">总计 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GRAND TOTAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">填写说明 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ How to use:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">蓝色字体单元格为填写项：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rate/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单价、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Time/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周期、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unit/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单位、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（数量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人数）；顶部黄色单元格填公司、日期、汇率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· RMB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列自动计算 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单价 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周期 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（周期或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">留空时按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">计）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -363,98 +1065,63 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">计价，具体日期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">酒店待确认</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">200102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">住宿 / Accommodation — 第二段</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中段，USD 计价，具体日期/酒店待确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">住宿 / Accommodation — 第三段</t>
-  </si>
-  <si>
-    <t xml:space="preserve">至 9.22，USD 计价，具体日期/酒店待确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当地杂费 LOCAL &amp; MISC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">餐饮 / Food &amp; Per Diem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按天计，待填</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当地交通 / Local Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">待填</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">签证费 / Visa Fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加拿大签证，待填</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不可预见费 CONTINGENCY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">比例可调整</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总计 GRAND TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">填写说明 / How to use:</t>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">计价行另乘 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">汇率；比例列 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">该行金额 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">总计，自动更新。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -472,248 +1139,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">蓝色字体单元格为填写项：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rate/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">单价、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Time/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周期、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Unit/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">单位、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（数量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人数）；顶部黄色单元格填公司、日期。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· RMB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列自动计算 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">单价 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周期 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（周期或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">留空时按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">计）；比例列 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">该行金额 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">总计，自动更新。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">机票金额（色珍 </t>
     </r>
     <r>
@@ -765,24 +1190,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；住宿分段金额（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">760 / 900 / 3,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">；住宿为 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Airbnb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整租 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$5,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
     </r>
     <r>
       <rPr>
@@ -816,75 +1258,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">晚）为 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">USD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RMB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= USD </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">金额 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× B6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汇率（默认 </t>
+      <t xml:space="preserve">晚，约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$384.6/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晚），汇率默认 </t>
     </r>
     <r>
       <rPr>
@@ -901,7 +1292,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">（</t>
     </r>
     <r>
       <rPr>
@@ -918,7 +1309,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">市场价，可修改）。</t>
+      <t xml:space="preserve">市场价，可在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">修改）。</t>
     </r>
   </si>
   <si>
@@ -986,7 +1394,7 @@
     <numFmt numFmtId="167" formatCode="0.00%"/>
     <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,6 +1422,12 @@
       <sz val="9"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1027,27 +1441,8 @@
       <sz val="9"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="0"/>
@@ -1088,7 +1483,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1103,6 +1497,12 @@
       <sz val="8"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1203,40 +1603,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,7 +1636,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,47 +1644,47 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1300,15 +1692,31 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1316,27 +1724,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1592,567 +1984,497 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="5" t="n">
         <v>6.73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="12" t="n">
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="10" t="n">
         <f aca="false">SUM(I9:I10)</f>
         <v>35000</v>
       </c>
-      <c r="J8" s="13" t="n">
-        <f aca="false">IF(OR($I8="",$I$24=0),"",$I8/$I$24)</f>
-        <v>0.464603270621184</v>
-      </c>
-      <c r="K8" s="11"/>
+      <c r="J8" s="11" t="n">
+        <f aca="false">IF(OR($I8="",$I$22=0),"",$I8/$I$22)</f>
+        <v>0.485554746297645</v>
+      </c>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="15" t="n">
         <v>19000</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="17" t="n">
         <f aca="false">IF($E9="","",$E9*IF($F9="",1,$F9)*IF($H9="",1,$H9))</f>
         <v>19000</v>
       </c>
-      <c r="J9" s="20" t="n">
-        <f aca="false">IF(OR($I9="",$I$24=0),"",$I9/$I$24)</f>
-        <v>0.2522132040515</v>
-      </c>
-      <c r="K9" s="15" t="s">
+      <c r="J9" s="18" t="n">
+        <f aca="false">IF(OR($I9="",$I$22=0),"",$I9/$I$22)</f>
+        <v>0.263586862275865</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="15" t="n">
         <v>16000</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="17" t="n">
         <f aca="false">IF($E10="","",$E10*IF($F10="",1,$F10)*IF($H10="",1,$H10))</f>
         <v>16000</v>
       </c>
-      <c r="J10" s="20" t="n">
-        <f aca="false">IF(OR($I10="",$I$24=0),"",$I10/$I$24)</f>
-        <v>0.212390066569684</v>
-      </c>
-      <c r="K10" s="15" t="s">
+      <c r="J10" s="18" t="n">
+        <f aca="false">IF(OR($I10="",$I$22=0),"",$I10/$I$22)</f>
+        <v>0.221967884021781</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="12" t="n">
-        <f aca="false">SUM(I13:I15)</f>
-        <v>36745.8</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <f aca="false">IF(OR($I12="",$I$24=0),"",$I12/$I$24)</f>
-        <v>0.487777681759769</v>
-      </c>
-      <c r="K12" s="11"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="10" t="n">
+        <f aca="false">SUM(I13:I13)</f>
+        <v>33650</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <f aca="false">IF(OR($I12="",$I$22=0),"",$I12/$I$22)</f>
+        <v>0.466826206083307</v>
+      </c>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17" t="n">
-        <v>760</v>
-      </c>
-      <c r="F13" s="18" t="n">
+      <c r="D13" s="14"/>
+      <c r="E13" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="17" t="n">
         <f aca="false">IF($E13="","",$E13*$B$6*IF($F13="",1,$F13)*IF($H13="",1,$H13))</f>
-        <v>5114.8</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <f aca="false">IF(OR($I13="",$I$24=0),"",$I13/$I$24)</f>
-        <v>0.0678957945306638</v>
-      </c>
-      <c r="K13" s="21" t="s">
+        <v>33650</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <f aca="false">IF(OR($I13="",$I$22=0),"",$I13/$I$22)</f>
+        <v>0.466826206083307</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="10" t="n">
+        <f aca="false">SUM(I16:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <f aca="false">IF(OR($I15="",$I$22=0),"",$I15/$I$22)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17" t="n">
-        <v>900</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <f aca="false">IF($E14="","",$E14*$B$6*IF($F14="",1,$F14)*IF($H14="",1,$H14))</f>
-        <v>6057</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <f aca="false">IF(OR($I14="",$I$24=0),"",$I14/$I$24)</f>
-        <v>0.080402914575786</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>40</v>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="17" t="str">
+        <f aca="false">IF($E16="","",$E16*IF($F16="",1,$F16)*IF($H16="",1,$H16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="18" t="str">
+        <f aca="false">IF(OR($I16="",$I$22=0),"",$I16/$I$22)</f>
+        <v/>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="16" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <f aca="false">IF($E15="","",$E15*$B$6*IF($F15="",1,$F15)*IF($H15="",1,$H15))</f>
-        <v>25574</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <f aca="false">IF(OR($I15="",$I$24=0),"",$I15/$I$24)</f>
-        <v>0.339478972653319</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17" t="str">
+        <f aca="false">IF($E17="","",$E17*IF($F17="",1,$F17)*IF($H17="",1,$H17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="18" t="str">
+        <f aca="false">IF(OR($I17="",$I$22=0),"",$I17/$I$22)</f>
+        <v/>
+      </c>
+      <c r="K17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="12" t="n">
-        <f aca="false">SUM(I18:I20)</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <f aca="false">IF(OR($I17="",$I$24=0),"",$I17/$I$24)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19" t="str">
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17" t="str">
         <f aca="false">IF($E18="","",$E18*IF($F18="",1,$F18)*IF($H18="",1,$H18))</f>
         <v/>
       </c>
-      <c r="J18" s="20" t="str">
-        <f aca="false">IF(OR($I18="",$I$24=0),"",$I18/$I$24)</f>
+      <c r="J18" s="18" t="str">
+        <f aca="false">IF(OR($I18="",$I$22=0),"",$I18/$I$22)</f>
         <v/>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B20" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19" t="str">
-        <f aca="false">IF($E19="","",$E19*IF($F19="",1,$F19)*IF($H19="",1,$H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="20" t="str">
-        <f aca="false">IF(OR($I19="",$I$24=0),"",$I19/$I$24)</f>
-        <v/>
-      </c>
-      <c r="K19" s="15" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="H20" s="20"/>
+      <c r="I20" s="23" t="n">
+        <f aca="false">($E20)*(I8+I12+I15)</f>
+        <v>3432.5</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <f aca="false">IF(OR($I20="",$I$22=0),"",$I20/$I$22)</f>
+        <v>0.0476190476190476</v>
+      </c>
+      <c r="K20" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19" t="str">
-        <f aca="false">IF($E20="","",$E20*IF($F20="",1,$F20)*IF($H20="",1,$H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="20" t="str">
-        <f aca="false">IF(OR($I20="",$I$24=0),"",$I20/$I$24)</f>
-        <v/>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="27" t="n">
+        <f aca="false">(I8+I12+I15)+I20</f>
+        <v>72082.5</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <f aca="false">IF($I$22=0,"",1)</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="29"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="25" t="n">
-        <f aca="false">($E22)*(I8+I12+I17)</f>
-        <v>3587.29</v>
-      </c>
-      <c r="J22" s="26" t="n">
-        <f aca="false">IF(OR($I22="",$I$24=0),"",$I22/$I$24)</f>
-        <v>0.0476190476190476</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="29" t="n">
-        <f aca="false">(I8+I12+I17)+I22</f>
-        <v>75333.09</v>
-      </c>
-      <c r="J24" s="30" t="n">
-        <f aca="false">IF($I$24=0,"",1)</f>
-        <v>1</v>
-      </c>
-      <c r="K24" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="A26" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
+      <c r="A27" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
+      <c r="A28" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A30:K30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
